--- a/artfynd/A 39389-2023 artfynd.xlsx
+++ b/artfynd/A 39389-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113355153</v>
+        <v>114824780</v>
       </c>
       <c r="B2" t="n">
-        <v>90129</v>
+        <v>90238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,21 +708,13 @@
           <t>(Pers.) Quél.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö Nartorp, Ög</t>
+          <t>Hammarsberg 230 m V, Skällvik, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -732,7 +724,7 @@
         <v>6471539</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Jan Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Nina Gad Burgman, Per Gero Berntsson, Fanny Nyberg</t>
+          <t>Jan Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 39389-2023 artfynd.xlsx
+++ b/artfynd/A 39389-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
